--- a/experiments/results/resnet34/CIFAR-100/DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/DICE/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -715,6 +715,55 @@
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=None,scale_th=5.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>90.01000000000001</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
